--- a/Supplement_Tables.xlsx
+++ b/Supplement_Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indiana.sharepoint.com/sites/msteams_070f46/Shared Documents/General/2025 - Patient Similarity Network/Experimental Results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\BRIDGE_ADRD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2407" documentId="11_3B0C98FAF08D1CF03C00ABE64C47B55C9C4611B7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B5DE316-37F7-4076-867F-74C3FC71C9B8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACA1CD9-143D-4E22-A2EF-44F04D335FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table1" sheetId="1" r:id="rId1"/>
@@ -4536,13 +4536,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -11784,10 +11784,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="46" t="s">
         <v>108</v>
       </c>
       <c r="C1" s="16"/>
@@ -11801,10 +11801,10 @@
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
-      <c r="N1" s="47" t="s">
+      <c r="N1" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="O1" s="47" t="s">
+      <c r="O1" s="46" t="s">
         <v>108</v>
       </c>
       <c r="P1" s="16"/>
@@ -11820,8 +11820,8 @@
       <c r="X1" s="5"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="48"/>
+      <c r="A2" s="46"/>
+      <c r="B2" s="47"/>
       <c r="C2" s="16" t="s">
         <v>166</v>
       </c>
@@ -11849,8 +11849,8 @@
       <c r="K2" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="48"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="47"/>
       <c r="P2" s="16" t="s">
         <v>166</v>
       </c>
@@ -11880,7 +11880,7 @@
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="48" t="s">
         <v>82</v>
       </c>
       <c r="B3" s="18" t="s">
@@ -11913,7 +11913,7 @@
       <c r="K3" s="5" t="s">
         <v>812</v>
       </c>
-      <c r="N3" s="46" t="s">
+      <c r="N3" s="48" t="s">
         <v>82</v>
       </c>
       <c r="O3" s="18" t="s">
@@ -11948,7 +11948,7 @@
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
+      <c r="A4" s="48"/>
       <c r="B4" s="7" t="s">
         <v>85</v>
       </c>
@@ -11979,7 +11979,7 @@
       <c r="K4" s="5" t="s">
         <v>800</v>
       </c>
-      <c r="N4" s="46"/>
+      <c r="N4" s="48"/>
       <c r="O4" s="7" t="s">
         <v>85</v>
       </c>
@@ -12012,7 +12012,7 @@
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A5" s="46"/>
+      <c r="A5" s="48"/>
       <c r="B5" s="7" t="s">
         <v>86</v>
       </c>
@@ -12043,7 +12043,7 @@
       <c r="K5" s="5" t="s">
         <v>796</v>
       </c>
-      <c r="N5" s="46"/>
+      <c r="N5" s="48"/>
       <c r="O5" s="7" t="s">
         <v>86</v>
       </c>
@@ -12076,7 +12076,7 @@
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A6" s="46"/>
+      <c r="A6" s="48"/>
       <c r="B6" s="7" t="s">
         <v>87</v>
       </c>
@@ -12107,7 +12107,7 @@
       <c r="K6" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="N6" s="46"/>
+      <c r="N6" s="48"/>
       <c r="O6" s="7" t="s">
         <v>87</v>
       </c>
@@ -12140,7 +12140,7 @@
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" s="46"/>
+      <c r="A7" s="48"/>
       <c r="B7" s="7" t="s">
         <v>88</v>
       </c>
@@ -12171,7 +12171,7 @@
       <c r="K7" s="5" t="s">
         <v>788</v>
       </c>
-      <c r="N7" s="46"/>
+      <c r="N7" s="48"/>
       <c r="O7" s="7" t="s">
         <v>88</v>
       </c>
@@ -12204,7 +12204,7 @@
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A8" s="46"/>
+      <c r="A8" s="48"/>
       <c r="B8" s="7" t="s">
         <v>89</v>
       </c>
@@ -12235,7 +12235,7 @@
       <c r="K8" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="N8" s="46"/>
+      <c r="N8" s="48"/>
       <c r="O8" s="7" t="s">
         <v>89</v>
       </c>
@@ -12268,7 +12268,7 @@
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A9" s="46"/>
+      <c r="A9" s="48"/>
       <c r="B9" s="7" t="s">
         <v>90</v>
       </c>
@@ -12299,7 +12299,7 @@
       <c r="K9" s="5" t="s">
         <v>792</v>
       </c>
-      <c r="N9" s="46"/>
+      <c r="N9" s="48"/>
       <c r="O9" s="7" t="s">
         <v>90</v>
       </c>
@@ -12332,7 +12332,7 @@
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="48" t="s">
         <v>83</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -12365,7 +12365,7 @@
       <c r="K10" s="5" t="s">
         <v>1031</v>
       </c>
-      <c r="N10" s="46" t="s">
+      <c r="N10" s="48" t="s">
         <v>83</v>
       </c>
       <c r="O10" s="7" t="s">
@@ -12400,7 +12400,7 @@
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A11" s="46"/>
+      <c r="A11" s="48"/>
       <c r="B11" s="7" t="s">
         <v>92</v>
       </c>
@@ -12431,7 +12431,7 @@
       <c r="K11" s="5" t="s">
         <v>1032</v>
       </c>
-      <c r="N11" s="46"/>
+      <c r="N11" s="48"/>
       <c r="O11" s="7" t="s">
         <v>92</v>
       </c>
@@ -12464,7 +12464,7 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="46"/>
+      <c r="A12" s="48"/>
       <c r="B12" s="7" t="s">
         <v>93</v>
       </c>
@@ -12495,7 +12495,7 @@
       <c r="K12" s="5" t="s">
         <v>1019</v>
       </c>
-      <c r="N12" s="46"/>
+      <c r="N12" s="48"/>
       <c r="O12" s="7" t="s">
         <v>93</v>
       </c>
@@ -12528,7 +12528,7 @@
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="46"/>
+      <c r="A13" s="48"/>
       <c r="B13" s="7" t="s">
         <v>94</v>
       </c>
@@ -12559,7 +12559,7 @@
       <c r="K13" s="5" t="s">
         <v>1018</v>
       </c>
-      <c r="N13" s="46"/>
+      <c r="N13" s="48"/>
       <c r="O13" s="7" t="s">
         <v>94</v>
       </c>
@@ -12592,7 +12592,7 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A14" s="46"/>
+      <c r="A14" s="48"/>
       <c r="B14" s="7" t="s">
         <v>95</v>
       </c>
@@ -12623,7 +12623,7 @@
       <c r="K14" s="5" t="s">
         <v>1028</v>
       </c>
-      <c r="N14" s="46"/>
+      <c r="N14" s="48"/>
       <c r="O14" s="7" t="s">
         <v>95</v>
       </c>
@@ -12656,7 +12656,7 @@
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" s="46"/>
+      <c r="A15" s="48"/>
       <c r="B15" s="7" t="s">
         <v>96</v>
       </c>
@@ -12687,7 +12687,7 @@
       <c r="K15" s="5" t="s">
         <v>1023</v>
       </c>
-      <c r="N15" s="46"/>
+      <c r="N15" s="48"/>
       <c r="O15" s="7" t="s">
         <v>96</v>
       </c>
@@ -12720,7 +12720,7 @@
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="46"/>
+      <c r="A16" s="48"/>
       <c r="B16" s="7" t="s">
         <v>97</v>
       </c>
@@ -12751,7 +12751,7 @@
       <c r="K16" s="5" t="s">
         <v>1040</v>
       </c>
-      <c r="N16" s="46"/>
+      <c r="N16" s="48"/>
       <c r="O16" s="7" t="s">
         <v>97</v>
       </c>
@@ -12784,7 +12784,7 @@
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A17" s="46"/>
+      <c r="A17" s="48"/>
       <c r="B17" s="7" t="s">
         <v>98</v>
       </c>
@@ -12815,7 +12815,7 @@
       <c r="K17" s="5" t="s">
         <v>1027</v>
       </c>
-      <c r="N17" s="46"/>
+      <c r="N17" s="48"/>
       <c r="O17" s="7" t="s">
         <v>98</v>
       </c>
@@ -12848,7 +12848,7 @@
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A18" s="46"/>
+      <c r="A18" s="48"/>
       <c r="B18" s="7" t="s">
         <v>113</v>
       </c>
@@ -12879,7 +12879,7 @@
       <c r="K18" s="5" t="s">
         <v>1036</v>
       </c>
-      <c r="N18" s="46"/>
+      <c r="N18" s="48"/>
       <c r="O18" s="7" t="s">
         <v>113</v>
       </c>
@@ -12912,7 +12912,7 @@
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A19" s="46" t="s">
+      <c r="A19" s="48" t="s">
         <v>107</v>
       </c>
       <c r="B19" s="7" t="s">
@@ -12945,7 +12945,7 @@
       <c r="K19" s="5" t="s">
         <v>1272</v>
       </c>
-      <c r="N19" s="46" t="s">
+      <c r="N19" s="48" t="s">
         <v>107</v>
       </c>
       <c r="O19" s="7" t="s">
@@ -12980,7 +12980,7 @@
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A20" s="46"/>
+      <c r="A20" s="48"/>
       <c r="B20" s="7" t="s">
         <v>100</v>
       </c>
@@ -13011,7 +13011,7 @@
       <c r="K20" s="5" t="s">
         <v>1251</v>
       </c>
-      <c r="N20" s="46"/>
+      <c r="N20" s="48"/>
       <c r="O20" s="7" t="s">
         <v>100</v>
       </c>
@@ -13044,7 +13044,7 @@
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A21" s="46"/>
+      <c r="A21" s="48"/>
       <c r="B21" s="7" t="s">
         <v>101</v>
       </c>
@@ -13075,7 +13075,7 @@
       <c r="K21" s="5" t="s">
         <v>1247</v>
       </c>
-      <c r="N21" s="46"/>
+      <c r="N21" s="48"/>
       <c r="O21" s="7" t="s">
         <v>101</v>
       </c>
@@ -13108,7 +13108,7 @@
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A22" s="46"/>
+      <c r="A22" s="48"/>
       <c r="B22" s="7" t="s">
         <v>102</v>
       </c>
@@ -13139,7 +13139,7 @@
       <c r="K22" s="5" t="s">
         <v>1252</v>
       </c>
-      <c r="N22" s="46"/>
+      <c r="N22" s="48"/>
       <c r="O22" s="7" t="s">
         <v>102</v>
       </c>
@@ -13172,7 +13172,7 @@
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A23" s="46"/>
+      <c r="A23" s="48"/>
       <c r="B23" s="7" t="s">
         <v>103</v>
       </c>
@@ -13203,7 +13203,7 @@
       <c r="K23" s="5" t="s">
         <v>1264</v>
       </c>
-      <c r="N23" s="46"/>
+      <c r="N23" s="48"/>
       <c r="O23" s="7" t="s">
         <v>103</v>
       </c>
@@ -13236,7 +13236,7 @@
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A24" s="46"/>
+      <c r="A24" s="48"/>
       <c r="B24" s="7" t="s">
         <v>104</v>
       </c>
@@ -13267,7 +13267,7 @@
       <c r="K24" s="5" t="s">
         <v>1260</v>
       </c>
-      <c r="N24" s="46"/>
+      <c r="N24" s="48"/>
       <c r="O24" s="7" t="s">
         <v>104</v>
       </c>
@@ -13300,7 +13300,7 @@
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A25" s="46"/>
+      <c r="A25" s="48"/>
       <c r="B25" s="7" t="s">
         <v>105</v>
       </c>
@@ -13331,7 +13331,7 @@
       <c r="K25" s="5" t="s">
         <v>1256</v>
       </c>
-      <c r="N25" s="46"/>
+      <c r="N25" s="48"/>
       <c r="O25" s="7" t="s">
         <v>105</v>
       </c>
@@ -13364,7 +13364,7 @@
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A26" s="46"/>
+      <c r="A26" s="48"/>
       <c r="B26" s="7" t="s">
         <v>106</v>
       </c>
@@ -13395,7 +13395,7 @@
       <c r="K26" s="5" t="s">
         <v>1268</v>
       </c>
-      <c r="N26" s="46"/>
+      <c r="N26" s="48"/>
       <c r="O26" s="7" t="s">
         <v>106</v>
       </c>
@@ -13428,10 +13428,10 @@
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A28" s="47" t="s">
+      <c r="A28" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="46" t="s">
         <v>108</v>
       </c>
       <c r="C28" s="16"/>
@@ -13445,10 +13445,10 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
-      <c r="N28" s="47" t="s">
+      <c r="N28" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="O28" s="47" t="s">
+      <c r="O28" s="46" t="s">
         <v>108</v>
       </c>
       <c r="P28" s="16"/>
@@ -13464,8 +13464,8 @@
       <c r="X28" s="5"/>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A29" s="47"/>
-      <c r="B29" s="48"/>
+      <c r="A29" s="46"/>
+      <c r="B29" s="47"/>
       <c r="C29" s="16" t="s">
         <v>166</v>
       </c>
@@ -13493,8 +13493,8 @@
       <c r="K29" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="N29" s="47"/>
-      <c r="O29" s="48"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="47"/>
       <c r="P29" s="16" t="s">
         <v>166</v>
       </c>
@@ -13524,7 +13524,7 @@
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A30" s="46" t="s">
+      <c r="A30" s="48" t="s">
         <v>82</v>
       </c>
       <c r="B30" s="18" t="s">
@@ -13557,7 +13557,7 @@
       <c r="K30" s="5" t="s">
         <v>811</v>
       </c>
-      <c r="N30" s="46" t="s">
+      <c r="N30" s="48" t="s">
         <v>82</v>
       </c>
       <c r="O30" s="18" t="s">
@@ -13592,7 +13592,7 @@
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A31" s="46"/>
+      <c r="A31" s="48"/>
       <c r="B31" s="7" t="s">
         <v>85</v>
       </c>
@@ -13623,7 +13623,7 @@
       <c r="K31" s="5" t="s">
         <v>799</v>
       </c>
-      <c r="N31" s="46"/>
+      <c r="N31" s="48"/>
       <c r="O31" s="7" t="s">
         <v>85</v>
       </c>
@@ -13656,7 +13656,7 @@
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A32" s="46"/>
+      <c r="A32" s="48"/>
       <c r="B32" s="7" t="s">
         <v>86</v>
       </c>
@@ -13687,7 +13687,7 @@
       <c r="K32" s="5" t="s">
         <v>795</v>
       </c>
-      <c r="N32" s="46"/>
+      <c r="N32" s="48"/>
       <c r="O32" s="7" t="s">
         <v>86</v>
       </c>
@@ -13720,7 +13720,7 @@
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A33" s="46"/>
+      <c r="A33" s="48"/>
       <c r="B33" s="7" t="s">
         <v>87</v>
       </c>
@@ -13751,7 +13751,7 @@
       <c r="K33" s="5" t="s">
         <v>803</v>
       </c>
-      <c r="N33" s="46"/>
+      <c r="N33" s="48"/>
       <c r="O33" s="7" t="s">
         <v>87</v>
       </c>
@@ -13784,7 +13784,7 @@
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A34" s="46"/>
+      <c r="A34" s="48"/>
       <c r="B34" s="7" t="s">
         <v>88</v>
       </c>
@@ -13815,7 +13815,7 @@
       <c r="K34" s="5" t="s">
         <v>787</v>
       </c>
-      <c r="N34" s="46"/>
+      <c r="N34" s="48"/>
       <c r="O34" s="7" t="s">
         <v>88</v>
       </c>
@@ -13848,7 +13848,7 @@
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A35" s="46"/>
+      <c r="A35" s="48"/>
       <c r="B35" s="7" t="s">
         <v>89</v>
       </c>
@@ -13879,7 +13879,7 @@
       <c r="K35" s="5" t="s">
         <v>807</v>
       </c>
-      <c r="N35" s="46"/>
+      <c r="N35" s="48"/>
       <c r="O35" s="7" t="s">
         <v>89</v>
       </c>
@@ -13912,7 +13912,7 @@
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A36" s="46"/>
+      <c r="A36" s="48"/>
       <c r="B36" s="7" t="s">
         <v>90</v>
       </c>
@@ -13943,7 +13943,7 @@
       <c r="K36" s="5" t="s">
         <v>791</v>
       </c>
-      <c r="N36" s="46"/>
+      <c r="N36" s="48"/>
       <c r="O36" s="7" t="s">
         <v>90</v>
       </c>
@@ -13976,7 +13976,7 @@
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A37" s="46" t="s">
+      <c r="A37" s="48" t="s">
         <v>83</v>
       </c>
       <c r="B37" s="7" t="s">
@@ -14009,7 +14009,7 @@
       <c r="K37" s="5" t="s">
         <v>1030</v>
       </c>
-      <c r="N37" s="46" t="s">
+      <c r="N37" s="48" t="s">
         <v>83</v>
       </c>
       <c r="O37" s="7" t="s">
@@ -14044,7 +14044,7 @@
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A38" s="46"/>
+      <c r="A38" s="48"/>
       <c r="B38" s="7" t="s">
         <v>92</v>
       </c>
@@ -14075,7 +14075,7 @@
       <c r="K38" s="5" t="s">
         <v>869</v>
       </c>
-      <c r="N38" s="46"/>
+      <c r="N38" s="48"/>
       <c r="O38" s="7" t="s">
         <v>92</v>
       </c>
@@ -14108,7 +14108,7 @@
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A39" s="46"/>
+      <c r="A39" s="48"/>
       <c r="B39" s="7" t="s">
         <v>93</v>
       </c>
@@ -14139,7 +14139,7 @@
       <c r="K39" s="5" t="s">
         <v>863</v>
       </c>
-      <c r="N39" s="46"/>
+      <c r="N39" s="48"/>
       <c r="O39" s="7" t="s">
         <v>93</v>
       </c>
@@ -14172,7 +14172,7 @@
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A40" s="46"/>
+      <c r="A40" s="48"/>
       <c r="B40" s="7" t="s">
         <v>94</v>
       </c>
@@ -14203,7 +14203,7 @@
       <c r="K40" s="5" t="s">
         <v>1017</v>
       </c>
-      <c r="N40" s="46"/>
+      <c r="N40" s="48"/>
       <c r="O40" s="7" t="s">
         <v>94</v>
       </c>
@@ -14236,7 +14236,7 @@
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A41" s="46"/>
+      <c r="A41" s="48"/>
       <c r="B41" s="7" t="s">
         <v>95</v>
       </c>
@@ -14267,7 +14267,7 @@
       <c r="K41" s="5" t="s">
         <v>1002</v>
       </c>
-      <c r="N41" s="46"/>
+      <c r="N41" s="48"/>
       <c r="O41" s="7" t="s">
         <v>95</v>
       </c>
@@ -14300,7 +14300,7 @@
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A42" s="46"/>
+      <c r="A42" s="48"/>
       <c r="B42" s="7" t="s">
         <v>96</v>
       </c>
@@ -14331,7 +14331,7 @@
       <c r="K42" s="5" t="s">
         <v>1022</v>
       </c>
-      <c r="N42" s="46"/>
+      <c r="N42" s="48"/>
       <c r="O42" s="7" t="s">
         <v>96</v>
       </c>
@@ -14364,7 +14364,7 @@
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A43" s="46"/>
+      <c r="A43" s="48"/>
       <c r="B43" s="7" t="s">
         <v>97</v>
       </c>
@@ -14395,7 +14395,7 @@
       <c r="K43" s="5" t="s">
         <v>1039</v>
       </c>
-      <c r="N43" s="46"/>
+      <c r="N43" s="48"/>
       <c r="O43" s="7" t="s">
         <v>97</v>
       </c>
@@ -14428,7 +14428,7 @@
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A44" s="46"/>
+      <c r="A44" s="48"/>
       <c r="B44" s="7" t="s">
         <v>98</v>
       </c>
@@ -14459,7 +14459,7 @@
       <c r="K44" s="5" t="s">
         <v>1026</v>
       </c>
-      <c r="N44" s="46"/>
+      <c r="N44" s="48"/>
       <c r="O44" s="7" t="s">
         <v>98</v>
       </c>
@@ -14492,7 +14492,7 @@
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A45" s="46"/>
+      <c r="A45" s="48"/>
       <c r="B45" s="7" t="s">
         <v>113</v>
       </c>
@@ -14523,7 +14523,7 @@
       <c r="K45" s="5" t="s">
         <v>1035</v>
       </c>
-      <c r="N45" s="46"/>
+      <c r="N45" s="48"/>
       <c r="O45" s="7" t="s">
         <v>113</v>
       </c>
@@ -14556,7 +14556,7 @@
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A46" s="46" t="s">
+      <c r="A46" s="48" t="s">
         <v>107</v>
       </c>
       <c r="B46" s="7" t="s">
@@ -14589,7 +14589,7 @@
       <c r="K46" s="5" t="s">
         <v>1271</v>
       </c>
-      <c r="N46" s="46" t="s">
+      <c r="N46" s="48" t="s">
         <v>107</v>
       </c>
       <c r="O46" s="7" t="s">
@@ -14624,7 +14624,7 @@
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A47" s="46"/>
+      <c r="A47" s="48"/>
       <c r="B47" s="7" t="s">
         <v>100</v>
       </c>
@@ -14655,7 +14655,7 @@
       <c r="K47" s="5" t="s">
         <v>1250</v>
       </c>
-      <c r="N47" s="46"/>
+      <c r="N47" s="48"/>
       <c r="O47" s="7" t="s">
         <v>100</v>
       </c>
@@ -14688,7 +14688,7 @@
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A48" s="46"/>
+      <c r="A48" s="48"/>
       <c r="B48" s="7" t="s">
         <v>101</v>
       </c>
@@ -14719,7 +14719,7 @@
       <c r="K48" s="5" t="s">
         <v>1246</v>
       </c>
-      <c r="N48" s="46"/>
+      <c r="N48" s="48"/>
       <c r="O48" s="7" t="s">
         <v>101</v>
       </c>
@@ -14752,7 +14752,7 @@
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A49" s="46"/>
+      <c r="A49" s="48"/>
       <c r="B49" s="7" t="s">
         <v>102</v>
       </c>
@@ -14783,7 +14783,7 @@
       <c r="K49" s="5" t="s">
         <v>967</v>
       </c>
-      <c r="N49" s="46"/>
+      <c r="N49" s="48"/>
       <c r="O49" s="7" t="s">
         <v>102</v>
       </c>
@@ -14816,7 +14816,7 @@
       </c>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A50" s="46"/>
+      <c r="A50" s="48"/>
       <c r="B50" s="7" t="s">
         <v>103</v>
       </c>
@@ -14847,7 +14847,7 @@
       <c r="K50" s="5" t="s">
         <v>1263</v>
       </c>
-      <c r="N50" s="46"/>
+      <c r="N50" s="48"/>
       <c r="O50" s="7" t="s">
         <v>103</v>
       </c>
@@ -14880,7 +14880,7 @@
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A51" s="46"/>
+      <c r="A51" s="48"/>
       <c r="B51" s="7" t="s">
         <v>104</v>
       </c>
@@ -14911,7 +14911,7 @@
       <c r="K51" s="5" t="s">
         <v>1259</v>
       </c>
-      <c r="N51" s="46"/>
+      <c r="N51" s="48"/>
       <c r="O51" s="7" t="s">
         <v>104</v>
       </c>
@@ -14944,7 +14944,7 @@
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A52" s="46"/>
+      <c r="A52" s="48"/>
       <c r="B52" s="7" t="s">
         <v>105</v>
       </c>
@@ -14975,7 +14975,7 @@
       <c r="K52" s="5" t="s">
         <v>1255</v>
       </c>
-      <c r="N52" s="46"/>
+      <c r="N52" s="48"/>
       <c r="O52" s="7" t="s">
         <v>105</v>
       </c>
@@ -15008,7 +15008,7 @@
       </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A53" s="46"/>
+      <c r="A53" s="48"/>
       <c r="B53" s="7" t="s">
         <v>106</v>
       </c>
@@ -15039,7 +15039,7 @@
       <c r="K53" s="5" t="s">
         <v>1267</v>
       </c>
-      <c r="N53" s="46"/>
+      <c r="N53" s="48"/>
       <c r="O53" s="7" t="s">
         <v>106</v>
       </c>
@@ -15073,26 +15073,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="A10:A18"/>
+    <mergeCell ref="A19:A26"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A30:A36"/>
+    <mergeCell ref="A37:A45"/>
+    <mergeCell ref="A46:A53"/>
+    <mergeCell ref="N28:N29"/>
+    <mergeCell ref="O28:O29"/>
+    <mergeCell ref="N30:N36"/>
+    <mergeCell ref="N37:N45"/>
+    <mergeCell ref="N46:N53"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
     <mergeCell ref="N3:N9"/>
     <mergeCell ref="N10:N18"/>
     <mergeCell ref="N19:N26"/>
-    <mergeCell ref="N28:N29"/>
-    <mergeCell ref="O28:O29"/>
-    <mergeCell ref="N30:N36"/>
-    <mergeCell ref="N37:N45"/>
-    <mergeCell ref="N46:N53"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A30:A36"/>
-    <mergeCell ref="A37:A45"/>
-    <mergeCell ref="A46:A53"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="A10:A18"/>
-    <mergeCell ref="A19:A26"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -40134,13 +40134,13 @@
       <c r="D4" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="38" t="s">
         <v>1311</v>
       </c>
       <c r="F4" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="38" t="s">
         <v>212</v>
       </c>
       <c r="H4" s="40" t="s">
@@ -40169,7 +40169,7 @@
       <c r="G5" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="H5" s="40" t="s">
+      <c r="H5" s="38" t="s">
         <v>247</v>
       </c>
     </row>
@@ -40293,7 +40293,7 @@
       <c r="E10" s="40" t="s">
         <v>1324</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F10" s="38" t="s">
         <v>1325</v>
       </c>
       <c r="G10" s="40" t="s">
@@ -50140,15 +50140,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A9095C626CCE4B449E545EEC892BBCFA" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8bd3e1af5b3741b1c0ab0efc01909e9b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b019dcc9-cfc8-400d-b696-bdbbc1c49ef2" xmlns:ns3="c2b53b0c-fec2-44ca-89f7-2555e448e9d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="40914927dd17d867a257da0571efe2f5" ns2:_="" ns3:_="">
     <xsd:import namespace="b019dcc9-cfc8-400d-b696-bdbbc1c49ef2"/>
@@ -50349,6 +50340,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -50362,14 +50362,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25FA01B5-F994-4F8F-BF7F-C5C72288C88E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90C98032-62A9-41F9-9259-FF135451AFFE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50384,6 +50376,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25FA01B5-F994-4F8F-BF7F-C5C72288C88E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
